--- a/templates/eml_metadata_from_sample.xlsx
+++ b/templates/eml_metadata_from_sample.xlsx
@@ -7,12 +7,15 @@
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="creators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="personnel" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="associated_parties" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -36,6 +39,7 @@
   </si>
   <si>
     <t xml:space="preserve">This dataset contains environmental DNA (eDNA) metabarcoding data generated through Minderoo OceanOmics Centre at UWA research projects. The dataset provides information on biological samples collected from marine environments, including sampling locations, collection details, molecular processing, and taxonomic information derived from DNA sequencing. These data support the study of marine biodiversity, species distributions, and environmental monitoring using eDNA approaches. The dataset has been processed and quality checked to support reproducible research and data sharing.
+This dataset reflects the contributions of a large team across sample collection, laboratory processing, and bioinformatic analysis. It was produced by the Minderoo OceanOmics Centre at UWA, in partnership with the Minderoo Foundation, The University of Western Australia (UWA), and the UWA Oceans Institute.
 [This dataset was processed using FAIRe2OBIS.]</t>
   </si>
   <si>
@@ -45,7 +49,7 @@
     <t xml:space="preserve">Keywords</t>
   </si>
   <si>
-    <t xml:space="preserve">metabarcoding, DNA, eDNA, OcOm_2408, OcOm_2408_16SFishD, 16SFishD, OceanOmics, Minderoo, The University of Western Australia, UWA, Minderoo OceanOmics Centre</t>
+    <t xml:space="preserve">metabarcoding, DNA, eDNA, OcOm_2408, OcOm_2408_16SFishD, 16SFishD, OceanOmics, Minderoo, The University of Western Australia, UWA, Minderoo OceanOmics Centre, Fish, Research Data</t>
   </si>
   <si>
     <t xml:space="preserve">Comma-separated</t>
@@ -111,66 +115,45 @@
     <t xml:space="preserve">e.g. AU</t>
   </si>
   <si>
-    <t xml:space="preserve">Creator - given name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creator - surname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bennett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creator - position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bioinformatics Research Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creator - email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adam.bennett@uwa.edu.au</t>
+    <t xml:space="preserve">Phone number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0452537745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional - shared by everyone listed, like the address</t>
   </si>
   <si>
     <t xml:space="preserve">Metadata provider same as creator?</t>
   </si>
   <si>
+    <t xml:space="preserve">TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Creator" here means the FIRST row of the separate 'creators' sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metadata provider - given name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if not same as creator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metadata provider - surname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metadata provider - position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metadata provider - email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact same as creator?</t>
+  </si>
+  <si>
     <t xml:space="preserve">FALSE</t>
   </si>
   <si>
-    <t xml:space="preserve">Metadata provider - given name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only if not same as creator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metadata provider - surname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">De Jong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metadata provider - position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research Fellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metadata provider - email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emma.dejong@uwa.edu.au</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact same as creator?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Contact - given name</t>
   </si>
   <si>
@@ -193,48 +176,6 @@
   </si>
   <si>
     <t xml:space="preserve">shannon.corrigan@uwa.edu.au</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include an associated party?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated party - given name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anushka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only if included</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated party - surname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dissanayaka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated party - position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Assistant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated party - email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anushka.dissanayaka@uwa.edu.au</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated party - role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUBLISHER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUBLISHER / AUTHOR / PROCESSOR / EDITOR / REVIEWER / OWNER</t>
   </si>
   <si>
     <t xml:space="preserve">Method steps</t>
@@ -339,16 +280,7 @@
     <t xml:space="preserve">org_country</t>
   </si>
   <si>
-    <t xml:space="preserve">creator_given</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creator_sur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creator_position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creator_email</t>
+    <t xml:space="preserve">org_phone</t>
   </si>
   <si>
     <t xml:space="preserve">mp_same</t>
@@ -381,24 +313,6 @@
     <t xml:space="preserve">contact_email</t>
   </si>
   <si>
-    <t xml:space="preserve">ap_include</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ap_given</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ap_sur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ap_position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ap_email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ap_role</t>
-  </si>
-  <si>
     <t xml:space="preserve">methods</t>
   </si>
   <si>
@@ -424,6 +338,63 @@
   </si>
   <si>
     <t xml:space="preserve">design_desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raes@minderoo.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minderoo Foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ayad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mayad@minderoo.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POINT_OF_CONTACT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bennett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adam.bennett@uwa.edu.au</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURATOR</t>
   </si>
 </sst>
 </file>
@@ -789,7 +760,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
@@ -803,7 +774,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -817,7 +788,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -831,7 +802,7 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
@@ -845,7 +816,7 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -859,7 +830,7 @@
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -873,7 +844,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -887,7 +858,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -901,7 +872,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -915,7 +886,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
@@ -929,7 +900,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -943,7 +914,7 @@
         <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -954,66 +925,66 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
@@ -1021,97 +992,97 @@
         <v>42</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" t="s">
         <v>55</v>
       </c>
-      <c r="C24" t="s">
-        <v>5</v>
-      </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25">
@@ -1125,7 +1096,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26">
@@ -1139,7 +1110,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27">
@@ -1147,13 +1118,13 @@
         <v>60</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
         <v>61</v>
       </c>
-      <c r="C27" t="s">
-        <v>5</v>
-      </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
@@ -1164,192 +1135,289 @@
         <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="C29" t="s">
         <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="C30" t="s">
         <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="C31" t="s">
         <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C35" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>81</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>89</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>91</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" t="s">
-        <v>133</v>
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/templates/eml_metadata_from_sample.xlsx
+++ b/templates/eml_metadata_from_sample.xlsx
@@ -1,187 +1,203 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/00121238_uwa_edu_au/Documents/Documents/Project Repositories/Faire2OBIS/faire2obis/templates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BDE9AAF316F88AA8E303CBF82FBF631C7DB4CA13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{532BAD8E-92C1-42C3-9750-D9FAB817A7CD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView minimized="1" xWindow="30510" yWindow="1710" windowWidth="21600" windowHeight="11265" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="metadata" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="creators" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="personnel" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="associated_parties" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="metadata" sheetId="1" r:id="rId1"/>
+    <sheet name="creators" sheetId="2" r:id="rId2"/>
+    <sheet name="personnel" sheetId="3" r:id="rId3"/>
+    <sheet name="associated_parties" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
-  <si>
-    <t xml:space="preserve">Field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dataset title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OcOm_2408_16SFishD</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Abstract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This dataset contains environmental DNA (eDNA) metabarcoding data generated through Minderoo OceanOmics Centre at UWA research projects. The dataset provides information on biological samples collected from marine environments, including sampling locations, collection details, molecular processing, and taxonomic information derived from DNA sequencing. These data support the study of marine biodiversity, species distributions, and environmental monitoring using eDNA approaches. The dataset has been processed and quality checked to support reproducible research and data sharing.
-This dataset reflects the contributions of a large team across sample collection, laboratory processing, and bioinformatic analysis. It was produced by the Minderoo OceanOmics Centre at UWA, in partnership with the Minderoo Foundation, The University of Western Australia (UWA), and the UWA Oceans Institute.
-[This dataset was processed using FAIRe2OBIS.]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One paragraph per line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keywords</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metabarcoding, DNA, eDNA, OcOm_2408, OcOm_2408_16SFishD, 16SFishD, OceanOmics, Minderoo, The University of Western Australia, UWA, Minderoo OceanOmics Centre, Fish, Research Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comma-separated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">License URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://creativecommons.org/licenses/by-nc/4.0/legalcode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One of the exact CC license URLs FAIRe2OBIS offers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publication date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project/organization website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.uwa.edu.au/oceans-institute/partnerships/minderoo-oceanomics-centre-at-uwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minderoo OceanOmics Centre at UWA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Street address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35 Stirling Hwy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crawley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State/region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e.g. AU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0452537745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional - shared by everyone listed, like the address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metadata provider same as creator?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Creator" here means the FIRST row of the separate 'creators' sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metadata provider - given name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only if not same as creator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metadata provider - surname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metadata provider - position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metadata provider - email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact same as creator?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact - given name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shannon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact - surname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact - position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Research Fellow, OceanOmics Centre Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact - email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shannon.corrigan@uwa.edu.au</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Method steps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental sample collection from designated marine sampling locations.
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="135">
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Dataset title</t>
+  </si>
+  <si>
+    <t>Marine fish eDNA metabarcoding from the Great Barrier Reef, Australia, October 2020</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>This dataset contains environmental DNA (eDNA) metabarcoding data generated through Minderoo OceanOmics Centre at UWA research projects. The dataset provides information on biological samples collected from marine environments, including sampling locations, collection details, molecular processing, and taxonomic information derived from DNA sequencing. These data support the study of marine biodiversity, species distributions, and environmental monitoring using eDNA approaches. The dataset has been processed and quality checked to support reproducible research and data sharing.
+This dataset reflects the contributions of a large team across sample collection, laboratory processing, and bioinformatic analysis. It was produced by the Minderoo OceanOmics Centre at UWA, in partnership with the Minderoo Foundation, The University of Western Australia (UWA), and the UWA Oceans Institute.</t>
+  </si>
+  <si>
+    <t>One paragraph per line</t>
+  </si>
+  <si>
+    <t>Keywords</t>
+  </si>
+  <si>
+    <t>metabarcoding, DNA, eDNA, OcOm_2408, OcOm_2408_16SFishD, 16SFishD, OceanOmics, Minderoo, The University of Western Australia, UWA, Minderoo OceanOmics Centre, Fish, Research Data</t>
+  </si>
+  <si>
+    <t>Comma-separated</t>
+  </si>
+  <si>
+    <t>License URL</t>
+  </si>
+  <si>
+    <t>https://creativecommons.org/licenses/by-nc/4.0/legalcode</t>
+  </si>
+  <si>
+    <t>One of the exact CC license URLs FAIRe2OBIS offers</t>
+  </si>
+  <si>
+    <t>Publication date</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>Project/organization website</t>
+  </si>
+  <si>
+    <t>https://www.uwa.edu.au/oceans-institute/partnerships/minderoo-oceanomics-centre-at-uwa</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>Organization name</t>
+  </si>
+  <si>
+    <t>Minderoo OceanOmics Centre at UWA</t>
+  </si>
+  <si>
+    <t>Street address</t>
+  </si>
+  <si>
+    <t>35 Stirling Hwy</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Crawley</t>
+  </si>
+  <si>
+    <t>State/region</t>
+  </si>
+  <si>
+    <t>WA</t>
+  </si>
+  <si>
+    <t>Country code</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>e.g. AU</t>
+  </si>
+  <si>
+    <t>Phone number</t>
+  </si>
+  <si>
+    <t>(+61 8) 6488 6000</t>
+  </si>
+  <si>
+    <t>Optional - shared by everyone listed, like the address</t>
+  </si>
+  <si>
+    <t>Metadata provider same as creator?</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>"Creator" here means the FIRST row of the separate 'creators' sheet</t>
+  </si>
+  <si>
+    <t>Metadata provider - given name</t>
+  </si>
+  <si>
+    <t>Emma</t>
+  </si>
+  <si>
+    <t>Only if not same as creator</t>
+  </si>
+  <si>
+    <t>Metadata provider - surname</t>
+  </si>
+  <si>
+    <t>de Jong</t>
+  </si>
+  <si>
+    <t>Metadata provider - position</t>
+  </si>
+  <si>
+    <t>Senior Research Fellow</t>
+  </si>
+  <si>
+    <t>Metadata provider - email</t>
+  </si>
+  <si>
+    <t>emma.dejong@uwa.edu.au</t>
+  </si>
+  <si>
+    <t>Contact same as creator?</t>
+  </si>
+  <si>
+    <t>Contact - given name</t>
+  </si>
+  <si>
+    <t>Shannon</t>
+  </si>
+  <si>
+    <t>Contact - surname</t>
+  </si>
+  <si>
+    <t>Corrigan</t>
+  </si>
+  <si>
+    <t>Contact - position</t>
+  </si>
+  <si>
+    <t>Principal Research Fellow, OceanOmics Centre Lead</t>
+  </si>
+  <si>
+    <t>Contact - email</t>
+  </si>
+  <si>
+    <t>shannon.corrigan@uwa.edu.au</t>
+  </si>
+  <si>
+    <t>Method steps</t>
+  </si>
+  <si>
+    <t>Environmental sample collection from designated marine sampling locations.
 Sample preservation and storage following established laboratory and field protocols.
 DNA extraction from collected environmental samples.
 PCR amplification of targeted genetic markers for metabarcoding.
@@ -192,217 +208,242 @@
 Preparation of biodiversity records for research, analysis, and data sharing.</t>
   </si>
   <si>
-    <t xml:space="preserve">One step per line, in order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study extent description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marine environments sampled as part of the OceanOmics research program. Sampling locations represent the geographic extent of the project and are associated with individual environmental samples and their corresponding collection metadata.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sampling description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental samples were collected from designated marine sampling locations for eDNA metabarcoding analysis. Samples were collected using standardised field sampling procedures and recorded with associated information such as sampling location, collection date, sample identifiers, and other relevant environmental and field metadata.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leave blank to omit the whole Project section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OceanOmics eDNA Metabarcoding Survey: OcOm_2408_16SFishD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project abstract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This project uses environmental DNA (eDNA) metabarcoding to investigate marine biodiversity and detect fish and other aquatic taxa from environmental samples. The project generates molecular biodiversity data through DNA extraction, amplification, and high-throughput sequencing, followed by bioinformatic processing and taxonomic assignment. The resulting data support biodiversity assessment, species detection, ecological research, and the development of standardised eDNA approaches for marine monitoring.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minderoo Foundation
-The University of Western Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study area description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The study covers marine environments sampled as part of the OceanOmics research program. Environmental samples were collected from designated marine sampling locations to characterise biodiversity using eDNA metabarcoding. Geographic information associated with individual samples provides the specific spatial context for the observations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The project is designed to assess marine biodiversity using an eDNA metabarcoding approach. Environmental samples are collected from defined sampling locations and processed using standardised molecular workflows, including DNA extraction, PCR amplification, and sequencing. Sequence data are subsequently analysed using bioinformatic and taxonomic workflows to identify detected organisms. The resulting information is linked to sample and collection metadata to support biodiversity assessment, ecological analysis, reproducibility, and future data integration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abstract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">keywords</t>
-  </si>
-  <si>
-    <t xml:space="preserve">license</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pub_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">distribution_url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org_address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org_city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org_admin_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org_country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org_phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mp_same</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mp_given</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mp_sur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mp_position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mp_email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact_same</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact_given</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact_sur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact_position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact_email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">methods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">study_extent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sampling_desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">project_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">project_title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">project_abstract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">study_area_desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design_desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Given name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raes@minderoo.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minderoo Foundation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ayad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mayad@minderoo.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POINT_OF_CONTACT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bennett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adam.bennett@uwa.edu.au</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CURATOR</t>
+    <t>One step per line, in order</t>
+  </si>
+  <si>
+    <t>Study extent description</t>
+  </si>
+  <si>
+    <t>Marine environments sampled as part of the OceanOmics research program. Sampling locations represent the geographic extent of the project and are associated with individual environmental samples and their corresponding collection metadata.</t>
+  </si>
+  <si>
+    <t>Sampling description</t>
+  </si>
+  <si>
+    <t>Environmental samples were collected from designated marine sampling locations for eDNA metabarcoding analysis. Samples were collected using standardised field sampling procedures and recorded with associated information such as sampling location, collection date, sample identifiers, and other relevant environmental and field metadata.</t>
+  </si>
+  <si>
+    <t>Project ID</t>
+  </si>
+  <si>
+    <t>OcOm_2408_16SFishD</t>
+  </si>
+  <si>
+    <t>Leave blank to omit the whole Project section</t>
+  </si>
+  <si>
+    <t>Project title</t>
+  </si>
+  <si>
+    <t>OceanOmics eDNA Metabarcoding Survey: OcOm_2408_16SFishD</t>
+  </si>
+  <si>
+    <t>Project abstract</t>
+  </si>
+  <si>
+    <t>This project uses environmental DNA (eDNA) metabarcoding to investigate marine biodiversity and detect fish and other aquatic taxa from environmental samples. The project generates molecular biodiversity data through DNA extraction, amplification, and high-throughput sequencing, followed by bioinformatic processing and taxonomic assignment. The resulting data support biodiversity assessment, species detection, ecological research, and the development of standardised eDNA approaches for marine monitoring.</t>
+  </si>
+  <si>
+    <t>Funding</t>
+  </si>
+  <si>
+    <t>Minderoo Foundation, The University of Western Australia</t>
+  </si>
+  <si>
+    <t>Study area description</t>
+  </si>
+  <si>
+    <t>The study covers marine environments sampled as part of the OceanOmics research program. Environmental samples were collected from designated marine sampling locations to characterise biodiversity using eDNA metabarcoding. Geographic information associated with individual samples provides the specific spatial context for the observations.</t>
+  </si>
+  <si>
+    <t>Design description</t>
+  </si>
+  <si>
+    <t>The project is designed to assess marine biodiversity using an eDNA metabarcoding approach. Environmental samples are collected from defined sampling locations and processed using standardised molecular workflows, including DNA extraction, PCR amplification, and sequencing. Sequence data are subsequently analysed using bioinformatic and taxonomic workflows to identify detected organisms. The resulting information is linked to sample and collection metadata to support biodiversity assessment, ecological analysis, reproducibility, and future data integration.</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>abstract</t>
+  </si>
+  <si>
+    <t>keywords</t>
+  </si>
+  <si>
+    <t>license</t>
+  </si>
+  <si>
+    <t>pub_date</t>
+  </si>
+  <si>
+    <t>distribution_url</t>
+  </si>
+  <si>
+    <t>org_name</t>
+  </si>
+  <si>
+    <t>org_address</t>
+  </si>
+  <si>
+    <t>org_city</t>
+  </si>
+  <si>
+    <t>org_admin_area</t>
+  </si>
+  <si>
+    <t>org_country</t>
+  </si>
+  <si>
+    <t>org_phone</t>
+  </si>
+  <si>
+    <t>mp_same</t>
+  </si>
+  <si>
+    <t>mp_given</t>
+  </si>
+  <si>
+    <t>mp_sur</t>
+  </si>
+  <si>
+    <t>mp_position</t>
+  </si>
+  <si>
+    <t>mp_email</t>
+  </si>
+  <si>
+    <t>contact_same</t>
+  </si>
+  <si>
+    <t>contact_given</t>
+  </si>
+  <si>
+    <t>contact_sur</t>
+  </si>
+  <si>
+    <t>contact_position</t>
+  </si>
+  <si>
+    <t>contact_email</t>
+  </si>
+  <si>
+    <t>methods</t>
+  </si>
+  <si>
+    <t>study_extent</t>
+  </si>
+  <si>
+    <t>sampling_desc</t>
+  </si>
+  <si>
+    <t>project_id</t>
+  </si>
+  <si>
+    <t>project_title</t>
+  </si>
+  <si>
+    <t>project_abstract</t>
+  </si>
+  <si>
+    <t>funding</t>
+  </si>
+  <si>
+    <t>study_area_desc</t>
+  </si>
+  <si>
+    <t>design_desc</t>
+  </si>
+  <si>
+    <t>Given name</t>
+  </si>
+  <si>
+    <t>Surname</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Organization</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Eric</t>
+  </si>
+  <si>
+    <t>Raes</t>
+  </si>
+  <si>
+    <t>raes@minderoo.org</t>
+  </si>
+  <si>
+    <t>Senior Advisor, Operations &amp; Ocean Health</t>
+  </si>
+  <si>
+    <t>Minderoo Foundation</t>
+  </si>
+  <si>
+    <t>Marcelle</t>
+  </si>
+  <si>
+    <t>Ayad</t>
+  </si>
+  <si>
+    <t>mayad@minderoo.org</t>
+  </si>
+  <si>
+    <t>Research Advisor, Molecular Appplication</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>POINT_OF_CONTACT</t>
+  </si>
+  <si>
+    <t>Anushka</t>
+  </si>
+  <si>
+    <t>Dissanayaka</t>
+  </si>
+  <si>
+    <t>anushka.dissanayaka@uwa.edu.au</t>
+  </si>
+  <si>
+    <t>Bioinformatics Research Assiatant</t>
+  </si>
+  <si>
+    <t>PUBLISHER</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Bennett</t>
+  </si>
+  <si>
+    <t>adam.bennett@uwa.edu.au</t>
+  </si>
+  <si>
+    <t>Bioinformatics Research Officer</t>
+  </si>
+  <si>
+    <t>CURATOR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -416,10 +457,18 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -444,20 +493,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -739,17 +800,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="40.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="9.14" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7265625" customWidth="1"/>
+    <col min="2" max="2" width="60.7265625" customWidth="1"/>
+    <col min="3" max="3" width="40.7265625" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -760,10 +821,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -774,10 +835,10 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -788,10 +849,10 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -802,10 +863,10 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -816,10 +877,10 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -830,10 +891,10 @@
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -844,10 +905,10 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -858,10 +919,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -872,10 +933,10 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -886,10 +947,10 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -900,10 +961,10 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -914,10 +975,10 @@
         <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -928,10 +989,10 @@
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -942,299 +1003,297 @@
         <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
         <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="203" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D27" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="1" max="2" width="16.7265625" customWidth="1"/>
+    <col min="3" max="3" width="28.7265625" customWidth="1"/>
+    <col min="4" max="4" width="22.7265625" customWidth="1"/>
+    <col min="5" max="5" width="24.7265625" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" customWidth="1"/>
+    <col min="7" max="8" width="14.7265625" customWidth="1"/>
+    <col min="9" max="9" width="12.7265625" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>23</v>
@@ -1249,27 +1308,27 @@
         <v>29</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="F2" t="s">
-        <v>113</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -1278,30 +1337,30 @@
         <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C3" t="s">
-        <v>116</v>
+        <v>120</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
+        <v>5</v>
       </c>
       <c r="G3" t="s">
         <v>26</v>
@@ -1310,118 +1369,139 @@
         <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{A1AB8E27-53FC-4115-8DD9-8760F5E9C44E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+    <col min="1" max="2" width="16.7265625" customWidth="1"/>
+    <col min="3" max="3" width="28.7265625" customWidth="1"/>
+    <col min="4" max="4" width="24.7265625" customWidth="1"/>
+    <col min="5" max="5" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+    <col min="1" max="2" width="16.7265625" customWidth="1"/>
+    <col min="3" max="3" width="28.7265625" customWidth="1"/>
+    <col min="4" max="4" width="24.7265625" customWidth="1"/>
+    <col min="5" max="5" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" t="s">
-        <v>121</v>
+        <v>126</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{B30EACC7-7F72-44FA-9876-6D76BD103350}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>